--- a/tabelas_classes_excel/Tabela_3-4_O_Bardo.xlsx
+++ b/tabelas_classes_excel/Tabela_3-4_O_Bardo.xlsx
@@ -435,9 +435,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-    </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -953,7 +950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1006,31 +1003,6 @@
           <t>C7</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>C8</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>C10</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>C11</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>C12</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1042,23 +1014,63 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nível Bônus Base de Ataque Fortitude</t>
+          <t>Nível</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Bônus Base de Ataque</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fortitude</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>Reflexos</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Vontade Especial</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Vontade</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Especial</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>1°</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>+0</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>+0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Música de bardo, conhecimento de bardo, música</t>
         </is>
       </c>
@@ -1066,73 +1078,108 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1°</t>
+          <t>2°</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>+0</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>+0</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>proteção, fascinar, inspirar coragem +1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>proteção, fascinar, inspirar coragem +1</t>
+          <t>3°</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Inspirar competência</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2°</t>
+          <t>4°</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>+0</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3°</t>
+          <t>5°</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1142,83 +1189,93 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Inspirar competência</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4°</t>
+          <t>6°</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sugestão</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5°</t>
+          <t>7°</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6°</t>
+          <t>8°</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+6/+1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1228,88 +1285,93 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sugestão</t>
+          <t>Inspirar coragem +2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7°</t>
+          <t>9°</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6/+1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Inspirar grandeza</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8°</t>
+          <t>10°</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>+6/+1</t>
+          <t>+7/+2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Inspirar coragem +2</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9°</t>
+          <t>11°</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+6/+1</t>
+          <t>+8/+3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1319,83 +1381,93 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Inspirar grandeza</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10°</t>
+          <t>12°</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>+7/+2</t>
+          <t>+9/+4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+8</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Melodia da libertação</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>11°</t>
+          <t>13°</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>+8/+3</t>
+          <t>+9/+4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+8</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>12°</t>
+          <t>14°</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>+9/+4</t>
+          <t>+10/+5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1405,88 +1477,93 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Melodia da libertação</t>
+          <t>Inspirar coragem +3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>13°</t>
+          <t>15°</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>+9/+4</t>
+          <t>+11/+6/+1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+9</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Inspirar heroísmo</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>14°</t>
+          <t>16°</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>+10/+5</t>
+          <t>+12/+7/+2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Inspirar coragem +3</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>15°</t>
+          <t>17°</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>+11/+6/+1</t>
+          <t>+12/+7/+2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1496,83 +1573,93 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Inspirar heroísmo</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16°</t>
+          <t>18°</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>+12/+7/+2</t>
+          <t>+13/+8/+3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+11</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Sugestão em massa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>17°</t>
+          <t>19°</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>+12/+7/+2</t>
+          <t>+14/+9/+4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>+11</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>18°</t>
+          <t>20°</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>+13/+8/+3</t>
+          <t>+15/+10/+5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1582,624 +1669,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>+11</t>
+          <t>+12</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>+11</t>
+          <t>+12</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sugestão em massa</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>19°</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>+14/+9/+4</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>+6</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>+11</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>+11</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>20°</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>+15/+10/+5</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>+6</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>+12</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>+12</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
           <t>Inspirar coragem +4</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Dado de Vida: d6.</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>jogador. Na maioria d</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>na Tabela 3-5: Magias</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Perícias de Classe</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>tidade de magias conh</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>As perícias de classe de um bardo (e a habilidade chave para cada perícia)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>da Tabela 3-5 são fix</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>são: Acrobacia (Des), Arte da Fuga (Des), Atuação (Car), Avaliação (Int), Blefar</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Quando alcançar</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>(Car), Concentração (Con), Conhecimento (todos, escolhidos individualmente)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>20°), um bardo será c</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>(Int), Decifrar Escrita (Int), Diplomacia (Car), Disfarces (Car), Equilíbrio (Des),</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>antigo do seu repertó</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Escalar (For), Esconder-se (Des), Falar Idioma (n/a), Furtividade (Des), Identificar</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>nova. O nível das mag</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Magia (Int), Natação (For), Obter Informação (Car), Ofícios (Int), Ouvir (Sab),</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>mente conseguirá subs</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Prestidigitação (Des), Profissão (Sab), Saltar (For), Sentir Motivação (Sab) e Usar</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>disponível. Por exemp</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Instrumento Mágico (Car). Consulte o Capítulo 4: Perícias para obter as descrições</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>nível 0 (dois níveis</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>das perícias.</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>são as magias de 2° n</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Pontos de Perícia no 1° nível: (6 + modificador de Inteligência) x 4.</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>uma única magia de ní</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Pontos de Perícia a cada nível subseqüente: 6 + modificador de Inteligên-</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>3° nível) por um efei</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>cia.</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>substituir uma única</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>no momento em que adq</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Características da Classe</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Conforme descrit</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Usar Armas e Armaduras: Um bardo sabe usar todas as armas simples, além</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>cedência. Ele é capaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>da espada longa, sabre, bastão, espada curta, arco curto e chicote. Os bardos sabem</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>assumindo que não ten</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>usar armaduras leves e escudos (exceto escudo de corpo).</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>exemplo, Gimble, um b</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>O bardo é capaz de conjurar suas magias usando armaduras leves sem sofrer</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>a cada dia (consulte</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>a chance de falha de magia arcana, pois os componentes gestuais necessários para</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>de nível 0: detectar</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>suas magias são relativamente simples. No entanto, similar a qualquer conjurador,</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Conhecidas do Bardo).</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>um bardo que utilize armaduras médias e pesadas sofrerá a chance de falha de magia</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>qualquer combinação d</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>arcana quando o efeito possuir componentes gestuais (a maioria). Um bardo multi-</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>as magias que irá con</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>dasse sofre normalmente a chance de falha de magia arcana para os efeitos arcanos</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Conhecimento de</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>provenientes das outras classes.</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>viajam de um lugar pa</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Magias: Um bardo conjura magias arcanas (o mesmo tipo das magias disponíveis</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>realizar um teste esp</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>para os feiticeiros e magos) da lista de magias de bardo. Ele é capaz de conjurar suas</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>ao seu nível na class</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>magias sem prepará-las com antecedência, diferente de um mago ou um clérigo</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>alguma informação rel</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>(veja a seguir). Todas as magias de bardo possuem um componente verbal (cantar,</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>ou seus lugares famos</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>recitar ou tocar um instrumento).</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>ele recebe +2 de bônu</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Para aprender ou conjurar uma magia, um bardo deve ter uma pontuação em</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Carisma igual ou superior a 10 + o nível da magia (Car 10 para magias de nível</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>CD Tipo de Conhecim</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>0, Car 11 para magias de 1° nível, etc.). A Classe de Dificuldade para os testes de</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>10 Comum, conhecido</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>resistência contra essas magias equivale a 10 + nível da magia + modificador de</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>minoria consider</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Carisma do bardo.</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>local.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Semelhante aos demais conjuradores, um bardo somente é capaz de conjurar</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>uma quantidade limitada de magias de cada nível por dia. Seu limite diário de magias</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>20 Incomum, mas dis</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>se encontra na Tabela 3-4: O Bardo. As magias adicionais do bardo são baseadas em</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>conhecido por al</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>um valor elevado de Carisma (consulte a Tabela 1-1: Modificadores de Habilidade</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>da região.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>e Magias Adicionais).</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>25 Obscuro, conheci</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Quando a Tabela 3-4 indicar que um bardo recebe 0 magias de um determinado</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>difícil de encon</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>nível (por exemplo, 0 magias de 1° nível para um bardo de 2° nível), ele recebe somen-</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>te as magias adicionais concedidas pelo seu valor de Carisma para aquele nível.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>A seleção de magias do bardo é extremamente limitada. Um bardo de 1° nível</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>30 Extremamente obs</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>conhece quatro magias de nível 0 (também chamadas de truques), a escolha do</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>por raras pessoa</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>esquecido pela m</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>apenas por indiv</t>
         </is>
       </c>
     </row>
